--- a/output/pdf_financials_xlsx/PMX.xlsx
+++ b/output/pdf_financials_xlsx/PMX.xlsx
@@ -5679,46 +5679,46 @@
         <v>2.590332</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.49385</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.49716</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.515423</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.658283</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.69845</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.690558</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.685345</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.677253</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.685345</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.723012</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.777258</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.774681</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.770646</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.777433</v>
       </c>
     </row>
     <row r="93">
@@ -9500,7 +9500,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10370,7 +10374,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -12120,7 +12128,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13580,7 +13592,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PMX.xlsx
+++ b/output/pdf_financials_xlsx/PMX.xlsx
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001858</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.190295</v>
+        <v>-0.192153</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.18697</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.190295</v>
+        <v>-0.192153</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.131224</v>
@@ -2379,52 +2379,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.174112</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.138416</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.095249</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.032719</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.032876</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.038061</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011686</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.027029</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.004952</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000947</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.004952</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.317853</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.070025</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.10298</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.004145</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.003198</v>
       </c>
     </row>
     <row r="35">
@@ -2489,52 +2489,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.016659</v>
+        <v>0.190771</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.005591</v>
+        <v>0.144007</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.002058</v>
+        <v>0.097307</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.000632</v>
+        <v>0.033351</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.000275</v>
+        <v>0.033151</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.000478</v>
+        <v>0.038539</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.000713</v>
+        <v>0.012399</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.00663</v>
+        <v>0.033659</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.001001</v>
+        <v>0.005953</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.000594</v>
+        <v>0.001541</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.001001</v>
+        <v>0.005953</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.000574</v>
+        <v>0.318427</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.000441</v>
+        <v>0.070466</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.000283</v>
+        <v>0.103263</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.000686</v>
+        <v>0.004831</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.001973</v>
+        <v>0.005171</v>
       </c>
     </row>
     <row r="37">
@@ -3149,52 +3149,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.176737</v>
+        <v>0.002625</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.142626</v>
+        <v>0.00421</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.095249</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.032805</v>
+        <v>8.6e-05</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.032876</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.038061</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.011686</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.027029</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.004952</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.000947</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.004952</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.322927</v>
+        <v>0.005074</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.07009899999999999</v>
+        <v>7.4e-05</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.103054</v>
+        <v>7.4e-05</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.004219</v>
+        <v>7.4e-05</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.003352</v>
+        <v>0.000154</v>
       </c>
     </row>
     <row r="49">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9018,7 +9018,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10854,7 +10858,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -11266,7 +11270,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -18320,7 +18328,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -45668,7 +45680,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" s="5" t="n">

--- a/output/pdf_financials_xlsx/PMX.xlsx
+++ b/output/pdf_financials_xlsx/PMX.xlsx
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.124875</v>
       </c>
       <c r="P112" s="3" t="n">
         <v>0</v>
@@ -18426,7 +18426,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
